--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D2">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="D3">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="H3">
         <v>426</v>
